--- a/src/main/resources/data.xlsx
+++ b/src/main/resources/data.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="cica" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="original" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t xml:space="preserve">birth date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alma</t>
+  </si>
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -37,36 +56,53 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
+    <t xml:space="preserve">2020.01.01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bob</t>
   </si>
   <si>
     <t xml:space="preserve">Canada</t>
   </si>
   <si>
+    <t xml:space="preserve">2020.01.02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Charlie</t>
   </si>
   <si>
     <t xml:space="preserve">UK</t>
   </si>
   <si>
+    <t xml:space="preserve">2020.01.03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diana</t>
   </si>
   <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
+    <t xml:space="preserve">2020.01.04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ethan</t>
   </si>
   <si>
     <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020.01.05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -136,12 +172,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -268,74 +312,54 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
+      <c r="A2" s="2" t="n">
+        <v>43834</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="E2" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -346,4 +370,107 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Normál"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normál"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normál"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/main/resources/data.xlsx
+++ b/src/main/resources/data.xlsx
@@ -21,7 +21,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
   <si>
     <t xml:space="preserve">birth date</t>
   </si>
@@ -185,7 +188,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -312,54 +315,537 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>43834</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="F2" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>43835</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="F3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>43836</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="F4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>43837</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="F5" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>123</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="E2" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
+      <c r="B6" s="2" t="n">
+        <v>43838</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="F6" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>43839</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>43840</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>43841</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>43842</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="F10" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>43843</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="F11" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>43844</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="F12" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>43845</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="F13" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>43846</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="F14" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>43847</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>43848</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="F16" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>43849</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="F17" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -382,86 +868,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
